--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-12 13:47</t>
+          <t>更新时间: 2026-08-12 14:02</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-12 14:02</t>
+          <t>更新时间: 2026-08-13 13:39</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-13 13:39</t>
+          <t>更新时间: 2026-08-13 13:52</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-14 13:50</t>
+          <t>更新时间: 2026-08-14 14:05</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-14 14:05</t>
+          <t>更新时间: 2026-08-14 14:59</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-14 16:41</t>
+          <t>更新时间: 2026-08-15 08:15</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-15 08:15</t>
+          <t>更新时间: 2026-08-15 11:10</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-15 11:10</t>
+          <t>更新时间: 2026-08-15 11:23</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-16 08:09</t>
+          <t>更新时间: 2026-08-16 11:29</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-17 08:09</t>
+          <t>更新时间: 2026-08-17 11:30</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-17 11:30</t>
+          <t>更新时间: 2026-08-17 11:37</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-17 11:37</t>
+          <t>更新时间: 2026-08-17 12:26</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-17 13:53</t>
+          <t>更新时间: 2026-08-18 08:14</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-18 08:14</t>
+          <t>更新时间: 2026-08-18 11:13</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-18 12:20</t>
+          <t>更新时间: 2026-08-18 13:15</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-18 13:15</t>
+          <t>更新时间: 2026-08-19 08:17</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-19 08:17</t>
+          <t>更新时间: 2026-08-19 11:26</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-19 11:26</t>
+          <t>更新时间: 2026-08-19 11:32</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-20 08:15</t>
+          <t>更新时间: 2026-08-20 11:15</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-20 11:15</t>
+          <t>更新时间: 2026-08-20 11:33</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-20 13:18</t>
+          <t>更新时间: 2026-08-21 08:15</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-21 08:15</t>
+          <t>更新时间: 2026-08-21 11:33</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-22 13:04</t>
+          <t>更新时间: 2026-08-23 08:10</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-23 08:10</t>
+          <t>更新时间: 2026-08-23 11:32</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-24 08:11</t>
+          <t>更新时间: 2026-08-24 11:37</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-24 11:37</t>
+          <t>更新时间: 2026-08-24 12:03</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-24 12:32</t>
+          <t>更新时间: 2026-08-24 13:57</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-24 13:57</t>
+          <t>更新时间: 2026-08-25 08:15</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-25 08:15</t>
+          <t>更新时间: 2026-08-25 11:27</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-25 12:24</t>
+          <t>更新时间: 2026-08-25 13:20</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-25 13:20</t>
+          <t>更新时间: 2026-08-26 08:13</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-26 08:13</t>
+          <t>更新时间: 2026-08-26 11:39</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-26 11:39</t>
+          <t>更新时间: 2026-08-26 12:00</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-26 12:25</t>
+          <t>更新时间: 2026-08-26 13:20</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-26 13:20</t>
+          <t>更新时间: 2026-08-28 14:25</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-28 15:06</t>
+          <t>更新时间: 2026-08-29 05:27</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-29 05:27</t>
+          <t>更新时间: 2026-08-29 07:37</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-29 07:37</t>
+          <t>更新时间: 2026-08-29 08:22</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-29 08:22</t>
+          <t>更新时间: 2026-08-29 09:05</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-29 10:24</t>
+          <t>更新时间: 2026-08-29 12:01</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-29 12:01</t>
+          <t>更新时间: 2026-08-30 07:47</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-30 07:47</t>
+          <t>更新时间: 2026-08-30 08:22</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-30 08:22</t>
+          <t>更新时间: 2026-08-30 09:05</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-30 09:05</t>
+          <t>更新时间: 2026-08-30 10:24</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-30 10:24</t>
+          <t>更新时间: 2026-08-30 12:01</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-30 12:01</t>
+          <t>更新时间: 2026-08-31 07:48</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-31 07:48</t>
+          <t>更新时间: 2026-08-31 08:22</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-31 08:22</t>
+          <t>更新时间: 2026-08-31 09:05</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-31 09:05</t>
+          <t>更新时间: 2026-08-31 10:24</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-31 10:24</t>
+          <t>更新时间: 2026-08-31 12:01</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-31 12:01</t>
+          <t>更新时间: 2026-09-01 07:51</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-01 07:51</t>
+          <t>更新时间: 2026-09-01 08:38</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-01 08:38</t>
+          <t>更新时间: 2026-09-01 09:09</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-01 09:09</t>
+          <t>更新时间: 2026-09-01 10:29</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-01 10:29</t>
+          <t>更新时间: 2026-09-01 12:02</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-01 12:02</t>
+          <t>更新时间: 2026-09-02 07:51</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-02 07:51</t>
+          <t>更新时间: 2026-09-02 08:35</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-02 08:35</t>
+          <t>更新时间: 2026-09-02 09:08</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-02 09:08</t>
+          <t>更新时间: 2026-09-02 10:41</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-02 10:41</t>
+          <t>更新时间: 2026-09-02 12:02</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-02 12:02</t>
+          <t>更新时间: 2026-09-03 07:53</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-03 07:53</t>
+          <t>更新时间: 2026-09-03 08:37</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-03 08:37</t>
+          <t>更新时间: 2026-09-03 09:09</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-03 09:09</t>
+          <t>更新时间: 2026-09-03 13:11</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-03 13:11</t>
+          <t>更新时间: 2026-09-03 13:32</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-03 13:32</t>
+          <t>更新时间: 2026-09-04 07:51</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-04 07:51</t>
+          <t>更新时间: 2026-09-04 08:34</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-04 08:34</t>
+          <t>更新时间: 2026-09-04 09:08</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-04 09:08</t>
+          <t>更新时间: 2026-09-04 10:29</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-04 10:29</t>
+          <t>更新时间: 2026-09-04 12:02</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-04 12:02</t>
+          <t>更新时间: 2026-09-05 07:49</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-05 07:49</t>
+          <t>更新时间: 2026-09-05 08:36</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-05 08:36</t>
+          <t>更新时间: 2026-09-05 09:09</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-05 09:09</t>
+          <t>更新时间: 2026-09-05 10:28</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-05 10:28</t>
+          <t>更新时间: 2026-09-05 12:01</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-05 12:01</t>
+          <t>更新时间: 2026-09-06 09:27</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-06 09:27</t>
+          <t>更新时间: 2026-09-06 12:42</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-06 12:42</t>
+          <t>更新时间: 2026-09-06 13:31</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-06 13:31</t>
+          <t>更新时间: 2026-09-06 15:10</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-06 15:10</t>
+          <t>更新时间: 2026-09-06 16:10</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-06 16:10</t>
+          <t>更新时间: 2026-09-07 09:28</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-07 09:28</t>
+          <t>更新时间: 2026-09-07 12:44</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-07 12:44</t>
+          <t>更新时间: 2026-09-07 13:42</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-07 13:42</t>
+          <t>更新时间: 2026-09-07 15:22</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-07 15:22</t>
+          <t>更新时间: 2026-09-07 16:42</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-07 16:42</t>
+          <t>更新时间: 2026-09-08 09:32</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-08 09:32</t>
+          <t>更新时间: 2026-09-08 12:40</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-08 12:40</t>
+          <t>更新时间: 2026-09-08 13:38</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-08 13:38</t>
+          <t>更新时间: 2026-09-08 15:17</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-08 15:17</t>
+          <t>更新时间: 2026-09-08 16:23</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-08 16:23</t>
+          <t>更新时间: 2026-09-09 09:36</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-09 09:36</t>
+          <t>更新时间: 2026-09-09 12:45</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-09 12:45</t>
+          <t>更新时间: 2026-09-09 13:45</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-09 13:45</t>
+          <t>更新时间: 2026-09-09 15:26</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-09 15:26</t>
+          <t>更新时间: 2026-09-09 16:25</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-09 16:25</t>
+          <t>更新时间: 2026-09-10 09:31</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-10 09:31</t>
+          <t>更新时间: 2026-09-10 12:45</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-10 12:45</t>
+          <t>更新时间: 2026-09-10 13:38</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-10 13:38</t>
+          <t>更新时间: 2026-09-10 15:21</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-10 15:21</t>
+          <t>更新时间: 2026-09-10 16:27</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-10 16:27</t>
+          <t>更新时间: 2026-09-11 09:35</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-11 09:35</t>
+          <t>更新时间: 2026-09-11 12:43</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-11 12:43</t>
+          <t>更新时间: 2026-09-11 13:38</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-11 13:38</t>
+          <t>更新时间: 2026-09-11 15:20</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-11 15:20</t>
+          <t>更新时间: 2026-09-11 16:22</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-11 16:22</t>
+          <t>更新时间: 2026-09-12 09:36</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-12 09:36</t>
+          <t>更新时间: 2026-09-12 12:38</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-12 12:38</t>
+          <t>更新时间: 2026-09-12 13:25</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-12 13:25</t>
+          <t>更新时间: 2026-09-12 15:12</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-12 15:12</t>
+          <t>更新时间: 2026-09-12 16:10</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-12 16:10</t>
+          <t>更新时间: 2026-09-13 09:33</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-13 09:33</t>
+          <t>更新时间: 2026-09-13 12:51</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-13 12:51</t>
+          <t>更新时间: 2026-09-13 13:40</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-13 13:40</t>
+          <t>更新时间: 2026-09-13 15:30</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-13 15:30</t>
+          <t>更新时间: 2026-09-13 16:35</t>
         </is>
       </c>
     </row>
